--- a/results/Supplementary/Appendix S4. Species germination x treatment formatted.xlsx
+++ b/results/Supplementary/Appendix S4. Species germination x treatment formatted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioviedo-my.sharepoint.com/personal/espinosaclara_uniovi_es/Documents/IMIB/Softwares/GitHub/Germination_drivers/results/supplementary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{12DE5730-3D3C-405E-A90C-7A48754F27E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51122054-9382-4BA5-8297-0230CCBC0631}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{12DE5730-3D3C-405E-A90C-7A48754F27E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84ABCE09-EFC3-49E9-B96B-D76A770FB1A8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9919D9C9-C261-40F3-A609-76256F7774B5}"/>
+    <workbookView xWindow="-11820" yWindow="135" windowWidth="11535" windowHeight="14745" xr2:uid="{9919D9C9-C261-40F3-A609-76256F7774B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S3. Species germination x" sheetId="1" r:id="rId1"/>
@@ -1362,25 +1362,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1796875" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" customWidth="1"/>
-    <col min="5" max="5" width="7.26953125" customWidth="1"/>
-    <col min="6" max="7" width="7.1796875" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" customWidth="1"/>
-    <col min="9" max="11" width="7.1796875" customWidth="1"/>
-    <col min="12" max="12" width="11.453125" customWidth="1"/>
-    <col min="13" max="15" width="7.1796875" customWidth="1"/>
-    <col min="16" max="16" width="11.453125" customWidth="1"/>
-    <col min="17" max="19" width="7.1796875" customWidth="1"/>
-    <col min="20" max="20" width="11.453125" customWidth="1"/>
-    <col min="21" max="22" width="7.1796875" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="11" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="13" max="15" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" customWidth="1"/>
+    <col min="17" max="19" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="21" max="22" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>72</v>
       </c>
@@ -1406,7 +1407,7 @@
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
     </row>
-    <row r="2" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>70</v>
       </c>
@@ -1432,7 +1433,7 @@
       <c r="U2" s="14"/>
       <c r="V2" s="14"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>68</v>
       </c>
@@ -1470,7 +1471,7 @@
       <c r="U3" s="20"/>
       <c r="V3" s="21"/>
     </row>
-    <row r="4" spans="1:22" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:22" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16"/>
       <c r="B4" s="18"/>
       <c r="C4" s="5" t="s">
@@ -1534,7 +1535,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -1602,7 +1603,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>9</v>
       </c>
@@ -1670,7 +1671,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>11</v>
       </c>
@@ -1738,7 +1739,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
@@ -1806,7 +1807,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
@@ -1874,7 +1875,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
@@ -1942,7 +1943,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
@@ -2078,7 +2079,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>17</v>
       </c>
@@ -2146,7 +2147,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>18</v>
       </c>
@@ -2214,7 +2215,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>19</v>
       </c>
@@ -2282,7 +2283,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
@@ -2350,7 +2351,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>21</v>
       </c>
@@ -2418,7 +2419,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>22</v>
       </c>
@@ -2486,7 +2487,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>23</v>
       </c>
@@ -2554,7 +2555,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>24</v>
       </c>
@@ -2622,7 +2623,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>25</v>
       </c>
@@ -2690,7 +2691,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>26</v>
       </c>
@@ -2758,7 +2759,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>27</v>
       </c>
@@ -2826,7 +2827,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>28</v>
       </c>
@@ -2894,7 +2895,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>29</v>
       </c>
@@ -2962,7 +2963,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>30</v>
       </c>
@@ -3030,7 +3031,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>31</v>
       </c>
@@ -3098,7 +3099,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>32</v>
       </c>
@@ -3166,7 +3167,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>33</v>
       </c>
@@ -3234,7 +3235,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>34</v>
       </c>
@@ -3302,7 +3303,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>35</v>
       </c>
@@ -3370,7 +3371,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>36</v>
       </c>
@@ -3438,7 +3439,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>37</v>
       </c>
@@ -3506,7 +3507,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>38</v>
       </c>
@@ -3574,7 +3575,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>39</v>
       </c>
@@ -3642,7 +3643,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>40</v>
       </c>
@@ -3710,7 +3711,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>41</v>
       </c>
@@ -3778,7 +3779,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>42</v>
       </c>
@@ -3846,7 +3847,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>43</v>
       </c>
@@ -3914,7 +3915,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>44</v>
       </c>
@@ -3982,7 +3983,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>45</v>
       </c>
@@ -4050,7 +4051,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>46</v>
       </c>
@@ -4118,7 +4119,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>47</v>
       </c>
@@ -4186,7 +4187,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>48</v>
       </c>
@@ -4254,7 +4255,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>49</v>
       </c>
@@ -4322,7 +4323,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>50</v>
       </c>
@@ -4390,7 +4391,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>51</v>
       </c>
@@ -4458,7 +4459,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>52</v>
       </c>
@@ -4526,7 +4527,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>53</v>
       </c>
@@ -4594,7 +4595,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>54</v>
       </c>
@@ -4662,7 +4663,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>55</v>
       </c>
@@ -4730,7 +4731,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>56</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>57</v>
       </c>
@@ -4866,7 +4867,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>58</v>
       </c>
@@ -4934,7 +4935,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>59</v>
       </c>
@@ -5002,7 +5003,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>60</v>
       </c>
@@ -5070,7 +5071,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>61</v>
       </c>
@@ -5138,7 +5139,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>62</v>
       </c>
@@ -5206,7 +5207,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>63</v>
       </c>
@@ -5274,7 +5275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>65</v>
       </c>
@@ -5342,7 +5343,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>65</v>
       </c>
@@ -5410,7 +5411,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="62" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>66</v>
       </c>

--- a/results/Supplementary/Appendix S4. Species germination x treatment formatted.xlsx
+++ b/results/Supplementary/Appendix S4. Species germination x treatment formatted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioviedo-my.sharepoint.com/personal/espinosaclara_uniovi_es/Documents/IMIB/Softwares/GitHub/Germination_drivers/results/supplementary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{12DE5730-3D3C-405E-A90C-7A48754F27E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84ABCE09-EFC3-49E9-B96B-D76A770FB1A8}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{12DE5730-3D3C-405E-A90C-7A48754F27E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11E1ED2E-E699-4149-BD40-BA0A2BAD1867}"/>
   <bookViews>
-    <workbookView xWindow="-11820" yWindow="135" windowWidth="11535" windowHeight="14745" xr2:uid="{9919D9C9-C261-40F3-A609-76256F7774B5}"/>
+    <workbookView xWindow="-19200" yWindow="0" windowWidth="14175" windowHeight="14745" xr2:uid="{9919D9C9-C261-40F3-A609-76256F7774B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S3. Species germination x" sheetId="1" r:id="rId1"/>
@@ -239,7 +239,7 @@
   </si>
   <si>
     <r>
-      <t>The Alpine Germination Syndrome differs between Temperate and Mediterranean habitats.</t>
+      <t xml:space="preserve">Supporting Information to the paper Espinosa del Alba et al., 2026. The Alpine Germination Syndrome differs between Temperate and Mediterranean habitats. </t>
     </r>
     <r>
       <rPr>
@@ -250,7 +250,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Journal of Vegetation Science</t>
+      <t>Journal of Vegetation Science</t>
     </r>
     <r>
       <rPr>
@@ -1366,18 +1366,18 @@
   <cols>
     <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="7.28515625" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" customWidth="1"/>
+    <col min="6" max="7" width="7.140625" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="11" width="7.140625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="13" max="15" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="9" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="13" max="15" width="7.140625" customWidth="1"/>
     <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="19" width="7.140625" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="21" max="22" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="17" max="19" width="7.140625" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" customWidth="1"/>
+    <col min="21" max="22" width="7.140625" customWidth="1"/>
     <col min="23" max="23" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
